--- a/fixtures/uploads/2026-09/cogm_card.xlsx
+++ b/fixtures/uploads/2026-09/cogm_card.xlsx
@@ -5707,7 +5707,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tidak</t>
+          <t>ya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
